--- a/readme.xlsx
+++ b/readme.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\TPS-Tanks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8118A621-F1EB-425B-A9F8-D68F8F814AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3193CB0B-4724-424C-956D-90FECEF85196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AC4DFB4C-03D2-451F-A124-4EF9D49EBC40}"/>
+    <workbookView xWindow="7368" yWindow="1860" windowWidth="17280" windowHeight="9960" xr2:uid="{AC4DFB4C-03D2-451F-A124-4EF9D49EBC40}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>readme</t>
     <phoneticPr fontId="1"/>
@@ -95,13 +95,6 @@
   </si>
   <si>
     <t>なし</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タンクのアセット変更</t>
-    <rPh sb="8" eb="10">
-      <t>ヘンコウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -112,13 +105,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>エネミー（ヘリ）追加</t>
-    <rPh sb="8" eb="10">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>備考</t>
     <rPh sb="0" eb="2">
       <t>ビコウ</t>
@@ -142,6 +128,117 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Assets/Scenes/TitleSceneを開くことでタイトルUIを確認できます。
+画面中央下部の白いボタンをクリックすることで、チュートリアル/ステージセレクトに遷移します。
+インゲームでescキーを押すことで、ポーズ画面を確認できます。
+Tutorialシーン内でDebugButton:GameClearをクリック後、再度画面中央下部の白いボタンをクリックすることで、ステージセレクトUIを確認できます。</t>
+    <rPh sb="25" eb="26">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カクニ</t>
+    </rPh>
+    <rPh sb="135" eb="136">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="163" eb="164">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="201" eb="203">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解放されていないステージのボタンをロックする機能は未実装</t>
+    <rPh sb="0" eb="2">
+      <t>カイホウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ミジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PC追加</t>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Assets/WorkSpace/Holy/HolyWorkSpaceを開くことで確認できます</t>
+    <rPh sb="36" eb="37">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズUI作成
+エネミー（ヘリ）追加</t>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルUI作成
+ステージセレクトUI作成</t>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>澁谷の確認方法を参照</t>
+    <rPh sb="0" eb="2">
+      <t>シブヤ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズ機能・UI適用
+タイトルUI適用
+ステージセレクトUI適用</t>
+    <rPh sb="3" eb="5">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テキヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -372,7 +469,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -382,9 +479,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -414,6 +508,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -753,8 +856,8 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -768,70 +871,72 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="8"/>
+      <c r="B5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:4" ht="36" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
+      <c r="B7" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>14</v>
+      <c r="D7" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:4" ht="54.6" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="13"/>
+      <c r="B8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
